--- a/MiniTemplate/Datas/convenience.xlsx
+++ b/MiniTemplate/Datas/convenience.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UGit\TimeChip\MiniTemplate\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Project\TimeChip\TimeChip\MiniTemplate\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{326D3E91-9858-4D40-9309-4DA5F7FE61B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{508059E6-E70D-4CA5-ACE1-055FC75FD3D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -460,17 +460,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G13"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="7.109375" customWidth="1"/>
-    <col min="3" max="3" width="18.88671875" customWidth="1"/>
-    <col min="4" max="4" width="20.6640625" customWidth="1"/>
-    <col min="5" max="5" width="11.88671875" customWidth="1"/>
-    <col min="6" max="6" width="15.88671875" customWidth="1"/>
-    <col min="7" max="7" width="21.44140625" customWidth="1"/>
+    <col min="2" max="2" width="7.125" customWidth="1"/>
+    <col min="3" max="3" width="18.875" customWidth="1"/>
+    <col min="4" max="4" width="20.625" customWidth="1"/>
+    <col min="5" max="5" width="11.875" customWidth="1"/>
+    <col min="6" max="6" width="15.875" customWidth="1"/>
+    <col min="7" max="7" width="21.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -493,7 +493,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -516,7 +516,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -539,7 +539,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -562,7 +562,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B5">
         <v>1</v>
       </c>
@@ -582,7 +582,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B6">
         <v>2</v>
       </c>
@@ -602,7 +602,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B7">
         <v>3</v>
       </c>
@@ -622,7 +622,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B8">
         <v>4</v>
       </c>
@@ -642,7 +642,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B9">
         <v>5</v>
       </c>
@@ -662,7 +662,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B10">
         <v>6</v>
       </c>
@@ -682,7 +682,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B11">
         <v>7</v>
       </c>
@@ -690,7 +690,7 @@
         <v>23</v>
       </c>
       <c r="D11">
-        <v>1010</v>
+        <v>102</v>
       </c>
       <c r="E11">
         <v>488</v>
@@ -702,7 +702,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B12">
         <v>8</v>
       </c>
@@ -710,7 +710,7 @@
         <v>23</v>
       </c>
       <c r="D12">
-        <v>1010</v>
+        <v>102</v>
       </c>
       <c r="E12">
         <v>688</v>
@@ -722,7 +722,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B13">
         <v>9</v>
       </c>
@@ -730,7 +730,7 @@
         <v>23</v>
       </c>
       <c r="D13">
-        <v>1010</v>
+        <v>102</v>
       </c>
       <c r="E13">
         <v>888</v>
